--- a/Employee_Reports_wi48/Regin Alis Q0187.xlsx
+++ b/Employee_Reports_wi48/Regin Alis Q0187.xlsx
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Control circuits (Cargo Trainings)</t>
+          <t>Weight scales (Cargo Trainings)</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -608,7 +608,7 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>LSME-CRG-M-019</t>
+          <t>LSME-CRG-M-013</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
@@ -618,20 +618,20 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>19-Feb-2026</t>
+          <t>09-Apr-2026</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>19-Feb-2028</t>
+          <t>08-Apr-2028</t>
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>586</v>
+        <v>632</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -647,122 +647,134 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
+          <t>Control circuits (Cargo Trainings)</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>CARGO</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>LSME-CRG-M-019</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>EQUIPMENT MANUAL</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>19-Feb-2026</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>19-Feb-2028</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>583</v>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
           <t>Powered roller Decks2 (Cargo Trainings)</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="3" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr"/>
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>18-Feb-2026</t>
         </is>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>18-Feb-2028</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
-        <v>585</v>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="H6" s="3" t="n">
+        <v>582</v>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Lodige LOTO Procedure (SOPs)</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>ELECTRICAL SAFETY</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>LSME-OHS-SOP-021</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>07-Oct-2024</t>
         </is>
       </c>
-      <c r="G6" s="4" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>07-Oct-2025</t>
         </is>
       </c>
-      <c r="H6" s="4" t="n">
-        <v>-279</v>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="H7" s="4" t="n">
+        <v>-282</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Endangered by Electricity A safety Training (SOPs)</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="3" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr">
-        <is>
-          <t>17-Nov-2025</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>17-Nov-2026</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="n">
-        <v>127</v>
-      </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -770,97 +782,85 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
+          <t>Endangered by Electricity A safety Training (SOPs)</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr"/>
+      <c r="D8" s="3" t="inlineStr"/>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>17-Nov-2025</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>17-Nov-2026</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>124</v>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
           <t>Misaligned Pallet-ULD Recovery Procedure (SOPs)</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D8" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-030</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>14-Jan-2026</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>14-Jan-2027</t>
         </is>
       </c>
-      <c r="H8" s="3" t="n">
-        <v>185</v>
-      </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Contigency Plan During Heavy Rainfall (SOPs)</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>IMS</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>LSME-IMS-SOP-018</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>09-Apr-2025</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>09-Apr-2026</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>-95</v>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>EXPIRED</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr"/>
+      <c r="H9" s="3" t="n">
+        <v>182</v>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -868,171 +868,195 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
+          <t>Contigency Plan During Heavy Rainfall (SOPs)</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-018</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>09-Apr-2025</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>09-Apr-2026</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>-98</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>EXPIRED</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr"/>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>10-Apr-2025</t>
         </is>
       </c>
-      <c r="G10" s="4" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>10-Apr-2026</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
-        <v>-94</v>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
+      <c r="H11" s="4" t="n">
+        <v>-97</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
         <is>
           <t>EXPIRED</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Replacement Procedure Of ASI Gateway (SOPs)</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>CARGO</t>
         </is>
       </c>
-      <c r="D11" s="3" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>LSME-CRG-SOP-041</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>23-Apr-2026</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>23-Apr-2027</t>
         </is>
       </c>
-      <c r="H11" s="3" t="n">
-        <v>284</v>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="H12" s="3" t="n">
+        <v>281</v>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Weight Scale Verification Procedure(LSME-IMS-SOP-023 ) (SOPs)</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>IMS</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>LSME-IMS-SOP-023</t>
         </is>
       </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>SOP</t>
         </is>
       </c>
-      <c r="F12" s="5" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>18-Jul-2025</t>
         </is>
       </c>
-      <c r="G12" s="5" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>18-Jul-2026</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="H13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>EXPIRING SOON</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr"/>
-      <c r="D13" s="3" t="inlineStr"/>
-      <c r="E13" s="3" t="inlineStr"/>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>30-Sep-2025</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>30-Sep-2026</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="n">
-        <v>79</v>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>12-Jul-2026</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>VALID</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr"/>
+      <c r="K13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1040,40 +1064,28 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Matar LOTO Procedure (SOPs)</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>MATAR</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>FM-DE-24-SOP-SA-013</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>SOP</t>
-        </is>
-      </c>
+          <t>NON POWERED ROLLER DECK(matarSOP) (SOPs)</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr"/>
+      <c r="D14" s="3" t="inlineStr"/>
+      <c r="E14" s="3" t="inlineStr"/>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>17-Nov-2025</t>
+          <t>30-Sep-2025</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>17-Nov-2026</t>
+          <t>30-Sep-2026</t>
         </is>
       </c>
       <c r="H14" s="3" t="n">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1089,28 +1101,40 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>20FT Floor Scale Weight Discrepancy Troubleshooting Guide (SOPs)</t>
-        </is>
-      </c>
-      <c r="C15" s="3" t="inlineStr"/>
-      <c r="D15" s="3" t="inlineStr"/>
-      <c r="E15" s="3" t="inlineStr"/>
+          <t>Matar LOTO Procedure (SOPs)</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>MATAR</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>FM-DE-24-SOP-SA-013</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>29-Jan-2026</t>
+          <t>17-Nov-2025</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>29-Jan-2027</t>
+          <t>17-Nov-2026</t>
         </is>
       </c>
       <c r="H15" s="3" t="n">
-        <v>200</v>
+        <v>124</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1126,7 +1150,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>PM Of CS H9 TV (SOPs)</t>
+          <t>20FT Floor Scale Weight Discrepancy Troubleshooting Guide (SOPs)</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr"/>
@@ -1134,20 +1158,20 @@
       <c r="E16" s="3" t="inlineStr"/>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>11-Jun-2026</t>
+          <t>29-Jan-2026</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>11-Jun-2027</t>
+          <t>29-Jan-2027</t>
         </is>
       </c>
       <c r="H16" s="3" t="n">
-        <v>333</v>
+        <v>197</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1163,7 +1187,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IS0 55001 (Other Trainings)</t>
+          <t>PM Of CS H9 TV (SOPs)</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr"/>
@@ -1171,20 +1195,20 @@
       <c r="E17" s="3" t="inlineStr"/>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2025</t>
+          <t>11-Jun-2026</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2027</t>
+          <t>11-Jun-2027</t>
         </is>
       </c>
       <c r="H17" s="3" t="n">
-        <v>364</v>
+        <v>330</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -1195,25 +1219,62 @@
       <c r="K17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr"/>
+      <c r="A18" s="3" t="n">
+        <v>16</v>
+      </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>YOU ARE LISTED AS ; SENIOR TECHNICIAN</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>&amp; THIS IS YOUR TRAINING DASHBOARD</t>
-        </is>
-      </c>
+          <t>IS0 55001 (Other Trainings)</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr"/>
       <c r="D18" s="3" t="inlineStr"/>
       <c r="E18" s="3" t="inlineStr"/>
-      <c r="F18" s="3" t="inlineStr"/>
-      <c r="G18" s="3" t="inlineStr"/>
-      <c r="H18" s="3" t="inlineStr"/>
-      <c r="I18" s="3" t="inlineStr"/>
-      <c r="J18" s="3" t="inlineStr"/>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>12-Jul-2025</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>12-Jul-2027</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>361</v>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t>15-Jul-2026</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>VALID</t>
+        </is>
+      </c>
       <c r="K18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>YOU ARE LISTED AS ; SENIOR TECHNICIAN</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>&amp; THIS IS YOUR TRAINING DASHBOARD</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr"/>
+      <c r="E19" s="3" t="inlineStr"/>
+      <c r="F19" s="3" t="inlineStr"/>
+      <c r="G19" s="3" t="inlineStr"/>
+      <c r="H19" s="3" t="inlineStr"/>
+      <c r="I19" s="3" t="inlineStr"/>
+      <c r="J19" s="3" t="inlineStr"/>
+      <c r="K19" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1433,7 +1494,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
@@ -1462,7 +1523,7 @@
         </is>
       </c>
       <c r="E4" s="3" t="n">
-        <v>7966</v>
+        <v>7963</v>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
@@ -1491,7 +1552,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n">
-        <v>7965</v>
+        <v>7962</v>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
@@ -1520,7 +1581,7 @@
         </is>
       </c>
       <c r="E6" s="3" t="n">
-        <v>7962</v>
+        <v>7959</v>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
@@ -1549,7 +1610,7 @@
         </is>
       </c>
       <c r="E7" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
@@ -1578,7 +1639,7 @@
         </is>
       </c>
       <c r="E8" s="3" t="n">
-        <v>7956</v>
+        <v>7953</v>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
@@ -1607,7 +1668,7 @@
         </is>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7959</v>
+        <v>7956</v>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
@@ -1636,7 +1697,7 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>7959</v>
+        <v>7956</v>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
@@ -1665,7 +1726,7 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>7962</v>
+        <v>7959</v>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
@@ -1694,7 +1755,7 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>7962</v>
+        <v>7959</v>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
@@ -1723,7 +1784,7 @@
         </is>
       </c>
       <c r="E13" s="3" t="n">
-        <v>7963</v>
+        <v>7960</v>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
@@ -1752,7 +1813,7 @@
         </is>
       </c>
       <c r="E14" s="3" t="n">
-        <v>7963</v>
+        <v>7960</v>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
@@ -1781,7 +1842,7 @@
         </is>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7955</v>
+        <v>7952</v>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
@@ -1810,7 +1871,7 @@
         </is>
       </c>
       <c r="E16" s="3" t="n">
-        <v>7955</v>
+        <v>7952</v>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
@@ -1839,7 +1900,7 @@
         </is>
       </c>
       <c r="E17" s="3" t="n">
-        <v>7966</v>
+        <v>7963</v>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
@@ -1868,7 +1929,7 @@
         </is>
       </c>
       <c r="E18" s="3" t="n">
-        <v>7966</v>
+        <v>7963</v>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
